--- a/Results/02_UVC_CPD_percentage_pvals_type.xlsx
+++ b/Results/02_UVC_CPD_percentage_pvals_type.xlsx
@@ -93,19 +93,19 @@
     <t>30 J/m²</t>
   </si>
   <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>300 J/m²</t>
+  </si>
+  <si>
+    <t>1000 J/m²</t>
+  </si>
+  <si>
     <t>**</t>
-  </si>
-  <si>
-    <t>***</t>
-  </si>
-  <si>
-    <t>300 J/m²</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>1000 J/m²</t>
   </si>
   <si>
     <t>2000 J/m²</t>
@@ -594,19 +594,19 @@
         <v>11</v>
       </c>
       <c r="I4">
-        <v>16.5</v>
+        <v>33.5</v>
       </c>
       <c r="J4">
-        <v>9.2100000000000005E-4</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="K4" t="s">
         <v>19</v>
       </c>
       <c r="L4">
-        <v>2.2048181818181802E-3</v>
+        <v>0.117169811320755</v>
       </c>
       <c r="M4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -644,10 +644,10 @@
         <v>19</v>
       </c>
       <c r="L5">
-        <v>4.8979999999999998E-4</v>
+        <v>7.4611999999999996E-4</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -676,19 +676,19 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="J6">
-        <v>9.1699999999999995E-4</v>
+        <v>1.15E-2</v>
       </c>
       <c r="K6" t="s">
         <v>19</v>
       </c>
       <c r="L6">
-        <v>2.2048181818181802E-3</v>
+        <v>2.9388888888888898E-2</v>
       </c>
       <c r="M6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -726,10 +726,10 @@
         <v>19</v>
       </c>
       <c r="L7">
-        <v>4.8979999999999998E-4</v>
+        <v>7.4611999999999996E-4</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -737,7 +737,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -761,16 +761,16 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>2.55E-5</v>
+        <v>4.49E-5</v>
       </c>
       <c r="K8" t="s">
         <v>19</v>
       </c>
       <c r="L8">
-        <v>4.8979999999999998E-4</v>
+        <v>7.4611999999999996E-4</v>
       </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -778,7 +778,7 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -808,10 +808,10 @@
         <v>19</v>
       </c>
       <c r="L9">
-        <v>4.8979999999999998E-4</v>
+        <v>7.4611999999999996E-4</v>
       </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -840,19 +840,19 @@
         <v>11</v>
       </c>
       <c r="I10">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="J10">
-        <v>9.2999999999999997E-5</v>
+        <v>1.2099999999999999E-3</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
       </c>
       <c r="L10">
-        <v>4.8979999999999998E-4</v>
+        <v>4.8399999999999997E-3</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -890,10 +890,10 @@
         <v>19</v>
       </c>
       <c r="L11">
-        <v>4.8979999999999998E-4</v>
+        <v>7.4611999999999996E-4</v>
       </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -978,7 +978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1004,16 +1004,16 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>30</v>
+        <v>45.5</v>
       </c>
       <c r="J14">
-        <v>3.5000000000000003E-2</v>
+        <v>0.746</v>
       </c>
       <c r="K14" t="s">
         <v>19</v>
       </c>
       <c r="L14">
-        <v>5.6428571428571397E-2</v>
+        <v>0.79804651162790696</v>
       </c>
       <c r="M14" t="s">
         <v>20</v>
@@ -1045,19 +1045,19 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J15">
-        <v>1.6900000000000001E-3</v>
+        <v>1.3899999999999999E-2</v>
       </c>
       <c r="K15" t="s">
         <v>19</v>
       </c>
       <c r="L15">
-        <v>3.8145714285714302E-3</v>
+        <v>3.4562162162162201E-2</v>
       </c>
       <c r="M15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -1086,19 +1086,19 @@
         <v>10</v>
       </c>
       <c r="I16">
+        <v>33</v>
+      </c>
+      <c r="J16">
+        <v>0.182</v>
+      </c>
+      <c r="K16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L16">
+        <v>0.27906666666666702</v>
+      </c>
+      <c r="M16" t="s">
         <v>20</v>
-      </c>
-      <c r="J16">
-        <v>5.94E-3</v>
-      </c>
-      <c r="K16" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16">
-        <v>1.0664999999999999E-2</v>
-      </c>
-      <c r="M16" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -1130,16 +1130,16 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>1.8000000000000001E-4</v>
+        <v>1.8100000000000001E-4</v>
       </c>
       <c r="K17" t="s">
         <v>19</v>
       </c>
       <c r="L17">
-        <v>6.8090476190476202E-4</v>
+        <v>9.8494117647058795E-4</v>
       </c>
       <c r="M17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -1147,7 +1147,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
@@ -1168,19 +1168,19 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J18">
-        <v>2.2000000000000001E-3</v>
+        <v>3.56E-2</v>
       </c>
       <c r="K18" t="s">
         <v>19</v>
       </c>
       <c r="L18">
-        <v>4.5736842105263201E-3</v>
+        <v>6.9469387755102002E-2</v>
       </c>
       <c r="M18" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
@@ -1218,10 +1218,10 @@
         <v>19</v>
       </c>
       <c r="L19">
-        <v>8.7977272727272698E-4</v>
+        <v>1.1863157894736801E-3</v>
       </c>
       <c r="M19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -1250,19 +1250,19 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="J20">
-        <v>7.4700000000000005E-4</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="K20" t="s">
         <v>19</v>
       </c>
       <c r="L20">
-        <v>1.9670999999999998E-3</v>
+        <v>3.9043902439024399E-2</v>
       </c>
       <c r="M20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -1291,24 +1291,24 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21">
-        <v>4.37E-4</v>
+        <v>3.28E-4</v>
       </c>
       <c r="K21" t="s">
         <v>19</v>
       </c>
       <c r="L21">
-        <v>1.27862962962963E-3</v>
+        <v>1.4369523809523799E-3</v>
       </c>
       <c r="M21" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <sortState ref="A2:M21">
-    <sortCondition ref="C1"/>
+    <sortCondition ref="C2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
